--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D50F03A-D11D-AE4F-B805-8A946BA4F8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363325FE-8C2D-FC4E-B8A1-30DCC94DC5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>53000</v>
+        <v>60000</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363325FE-8C2D-FC4E-B8A1-30DCC94DC5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9045187A-ABAE-C34E-AF06-6D186D3CD386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>60000</v>
+        <v>6000</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9045187A-ABAE-C34E-AF06-6D186D3CD386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27983266-ECA4-8B4F-8F19-D08B7771FF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27983266-ECA4-8B4F-8F19-D08B7771FF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3224C010-0C64-CC49-8AA9-D26D19BDECBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3224C010-0C64-CC49-8AA9-D26D19BDECBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390089A1-E25F-CC42-94CD-5C85915F32D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>600000</v>
+        <v>60</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390089A1-E25F-CC42-94CD-5C85915F32D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A674A4B9-52A3-2D4E-8EDB-D8E3264E6940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>60</v>
+        <v>6000</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A674A4B9-52A3-2D4E-8EDB-D8E3264E6940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6A447D-0A19-5D4E-B06A-05AD8389F3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>6000</v>
+        <v>60000</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6A447D-0A19-5D4E-B06A-05AD8389F3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3D76D8-AC14-E447-896E-32661FF2B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -806,7 +806,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="3">
-        <v>24500</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3D76D8-AC14-E447-896E-32661FF2B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E069577-0D2E-9945-BF62-11747630CDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -806,7 +806,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="3">
-        <v>24</v>
+        <v>24500</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E069577-0D2E-9945-BF62-11747630CDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06321A5D-E74F-E541-8C6D-8FD4B68BE6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>4800</v>
+        <v>800</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06321A5D-E74F-E541-8C6D-8FD4B68BE6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A856970-B475-944B-8F6C-6CE835013ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>800</v>
+        <v>9000</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A856970-B475-944B-8F6C-6CE835013ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D49A79-B586-3440-96C1-AD6EC750D385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D49A79-B586-3440-96C1-AD6EC750D385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBD504E-5699-9B4E-85C9-6245B5DFD8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>9000</v>
+        <v>900</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBD504E-5699-9B4E-85C9-6245B5DFD8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4262CC3-365E-EC4C-B225-FC45720D9C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijkrasnanskij/Desktop/КОЛЬКУЛЯТОР/files/calc-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4262CC3-365E-EC4C-B225-FC45720D9C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FABF957-B0FB-1C40-9C8C-FEB870E06160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>60000</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
